--- a/workshop_registration_form_templates/019_kayaking_safety_course_registration_form--workshop_registration_form_templates.xlsx
+++ b/workshop_registration_form_templates/019_kayaking_safety_course_registration_form--workshop_registration_form_templates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -510,12 +510,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_header</t>
+          <t>header</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Registration_Form</t>
+          <t>Form Header</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -533,18 +533,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>participant_details</t>
+          <t>participant_details_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Participant_Details</t>
+          <t>Participant Details 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>participant_details</t>
+          <t>participant_details_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Participant_Details</t>
+          <t>Participant Details 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -579,12 +579,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>participant_details</t>
+          <t>participant_details_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Participant_Details</t>
+          <t>Participant Details 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>participant_details</t>
+          <t>participant_details_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Participant_Details</t>
+          <t>Participant Details 4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -625,18 +625,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>waiver</t>
+          <t>waiver_agreement</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Waiver</t>
+          <t>Waiver Agreement</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Emergency_Contact</t>
+          <t>Emergency Contact</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -683,6 +683,282 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>participant_details_5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Additional Notes</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>participant_details_6</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>participant_details_7</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Medical Conditions</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>participant_details_8</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Participant's Phone</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>participant_details_9</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Participant's Email</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>submit_form</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Submit Form</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>form_conclusion</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>participant_details_10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Emergency Contact Info</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>participant_details_11</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Participant's Age</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>participant_details_12</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Participant's Date of Birth</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>submit_2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Submit 2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>form_conclusion_2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Thank You!</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
